--- a/results/standard/UNEP-EGR-2026-total-uncertainties.xlsx
+++ b/results/standard/UNEP-EGR-2026-total-uncertainties.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">CO2 Fossil</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6 ± 3.2</t>
+    <t xml:space="preserve">40 ± 3.2</t>
   </si>
   <si>
     <t xml:space="preserve">GtCO2e/year (GWP100 AR6)</t>
@@ -78,25 +78,25 @@
     <t xml:space="preserve">N2O</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6 ± 1.6</t>
+    <t xml:space="preserve">3 ± 1.8</t>
   </si>
   <si>
     <t xml:space="preserve">F-gases</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7 ± 0.52</t>
+    <t xml:space="preserve">2.1 ± 0.62</t>
   </si>
   <si>
     <t xml:space="preserve">CO2 LULUCF</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6 ± 3.2</t>
+    <t xml:space="preserve">4 ± 2.8</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9 ± 5.6</t>
+    <t xml:space="preserve">58.3 ± 5.4</t>
   </si>
 </sst>
 </file>
@@ -493,19 +493,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>39.6326790522035</v>
+        <v>39.9618316749995</v>
       </c>
       <c r="D2" t="n">
         <v>0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>3.17061432417628</v>
+        <v>3.19694653399996</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -516,19 +516,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9.28770527480275</v>
+        <v>9.29541434951061</v>
       </c>
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
       <c r="E3" t="n">
-        <v>2.78631158244082</v>
+        <v>2.78862430485318</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
@@ -539,19 +539,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>2.60373861103994</v>
+        <v>2.9511949975099</v>
       </c>
       <c r="D4" t="n">
         <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1.56224316662397</v>
+        <v>1.77071699850594</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -562,19 +562,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7472793606983</v>
+        <v>2.05515984744207</v>
       </c>
       <c r="D5" t="n">
         <v>0.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.524183808209491</v>
+        <v>0.616547954232621</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
@@ -585,19 +585,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58884259777778</v>
+        <v>4.0304</v>
       </c>
       <c r="D6" t="n">
         <v>0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3.21218981844444</v>
+        <v>2.82128</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -608,17 +608,17 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>57.8602448965222</v>
+        <v>58.2940008694621</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
-        <v>5.55426531894958</v>
+        <v>5.42881972089133</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
